--- a/artfynd/A 28769-2022 artfynd.xlsx
+++ b/artfynd/A 28769-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28769-2022 artfynd.xlsx
+++ b/artfynd/A 28769-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10622,6 +10622,115 @@
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129218118</v>
+      </c>
+      <c r="B89" t="n">
+        <v>91522</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Ruvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>368107</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6940826</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Herbert Baumann</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Herbert Baumann, Kerstin Baumann</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28769-2022 artfynd.xlsx
+++ b/artfynd/A 28769-2022 artfynd.xlsx
@@ -10627,7 +10627,7 @@
         <v>129218118</v>
       </c>
       <c r="B89" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 28769-2022 artfynd.xlsx
+++ b/artfynd/A 28769-2022 artfynd.xlsx
@@ -10627,7 +10627,7 @@
         <v>129218118</v>
       </c>
       <c r="B89" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 28769-2022 artfynd.xlsx
+++ b/artfynd/A 28769-2022 artfynd.xlsx
@@ -10627,7 +10627,7 @@
         <v>129218118</v>
       </c>
       <c r="B89" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Herbert Baumann, Kerstin Baumann</t>
+          <t>Kerstin Baumann, Herbert Baumann</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>

--- a/artfynd/A 28769-2022 artfynd.xlsx
+++ b/artfynd/A 28769-2022 artfynd.xlsx
@@ -10726,7 +10726,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kerstin Baumann, Herbert Baumann</t>
+          <t>Herbert Baumann, Kerstin Baumann</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>

--- a/artfynd/A 28769-2022 artfynd.xlsx
+++ b/artfynd/A 28769-2022 artfynd.xlsx
@@ -10627,7 +10627,7 @@
         <v>129218118</v>
       </c>
       <c r="B89" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 28769-2022 artfynd.xlsx
+++ b/artfynd/A 28769-2022 artfynd.xlsx
@@ -10627,7 +10627,7 @@
         <v>129218118</v>
       </c>
       <c r="B89" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 28769-2022 artfynd.xlsx
+++ b/artfynd/A 28769-2022 artfynd.xlsx
@@ -10627,7 +10627,7 @@
         <v>129218118</v>
       </c>
       <c r="B89" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Herbert Baumann, Kerstin Baumann</t>
+          <t>Kerstin Baumann, Herbert Baumann</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>

--- a/artfynd/A 28769-2022 artfynd.xlsx
+++ b/artfynd/A 28769-2022 artfynd.xlsx
@@ -10627,7 +10627,7 @@
         <v>129218118</v>
       </c>
       <c r="B89" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kerstin Baumann, Herbert Baumann</t>
+          <t>Herbert Baumann, Kerstin Baumann</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>

--- a/artfynd/A 28769-2022 artfynd.xlsx
+++ b/artfynd/A 28769-2022 artfynd.xlsx
@@ -10627,7 +10627,7 @@
         <v>129218118</v>
       </c>
       <c r="B89" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 28769-2022 artfynd.xlsx
+++ b/artfynd/A 28769-2022 artfynd.xlsx
@@ -10627,7 +10627,7 @@
         <v>129218118</v>
       </c>
       <c r="B89" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 28769-2022 artfynd.xlsx
+++ b/artfynd/A 28769-2022 artfynd.xlsx
@@ -10627,7 +10627,7 @@
         <v>129218118</v>
       </c>
       <c r="B89" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 28769-2022 artfynd.xlsx
+++ b/artfynd/A 28769-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1048523</v>
+        <v>129218118</v>
       </c>
       <c r="B2" t="n">
-        <v>89448</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3277</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vivallen NNV, mellan Vivallen och Ruvallen, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>368177.6698190488</v>
+        <v>368107</v>
       </c>
       <c r="R2" t="n">
-        <v>6940846.744621241</v>
+        <v>6940826</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1979-08-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1979-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Leg. Stig Jacobsson.</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,81 +765,68 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog med inslag av lövträd</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Herbert Baumann</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stig Jacobsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Stig Jacobssons dagböcker</t>
-        </is>
-      </c>
+          <t>Herbert Baumann, Kerstin Baumann</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1311820</v>
+        <v>102146309</v>
       </c>
       <c r="B3" t="n">
-        <v>90318</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vivallen NNV, mellan Vivallen och Ruvallen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>368177.6698190488</v>
+        <v>368259</v>
       </c>
       <c r="R3" t="n">
-        <v>6940846.744621241</v>
+        <v>6940706</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,27 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1979-08-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1979-08-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Leg. Stig Jacobsson.</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,40 +867,25 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrskog med inslag av lövträd</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stig Jacobsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Stig Jacobssons dagböcker</t>
-        </is>
-      </c>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1064323</v>
+        <v>102146848</v>
       </c>
       <c r="B4" t="n">
-        <v>85328</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,37 +893,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3528</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitterspindling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius agathosmus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brandrud, H.Lindstr. &amp; Melot</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vivallen NNV, mellan Vivallen och Ruvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>368177.6698190488</v>
+        <v>368092</v>
       </c>
       <c r="R4" t="n">
-        <v>6940846.744621241</v>
+        <v>6940806</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,27 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2005-08-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2005-08-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Leg. Stig Jacobsson.</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,40 +965,25 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrskog med inslag av lövträd</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stig Jacobsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Stig Jacobssons dagböcker</t>
-        </is>
-      </c>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1232067</v>
+        <v>102146864</v>
       </c>
       <c r="B5" t="n">
-        <v>85453</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,37 +991,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3639</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rutspindling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius ionophyllus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vivallen NNV, mellan Vivallen och Ruvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>368177.6698190488</v>
+        <v>368069</v>
       </c>
       <c r="R5" t="n">
-        <v>6940846.744621241</v>
+        <v>6940814</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,27 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2005-08-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2005-08-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Leg. Stig Jacobsson.</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,40 +1063,25 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrskog med inslag av lövträd</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stig Jacobsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Stig Jacobssons dagböcker</t>
-        </is>
-      </c>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102147511</v>
+        <v>102147811</v>
       </c>
       <c r="B6" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1224,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>367859.5718283363</v>
+        <v>367830</v>
       </c>
       <c r="R6" t="n">
-        <v>6940969.691933472</v>
+        <v>6940949</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1257,19 +1147,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,15 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102151426</v>
+        <v>102148453</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1312,35 +1187,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>368293.6792303553</v>
+        <v>367833</v>
       </c>
       <c r="R7" t="n">
-        <v>6940765.996210388</v>
+        <v>6941063</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1370,19 +1245,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,15 +1274,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102146201</v>
+        <v>102149019</v>
       </c>
       <c r="B8" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,35 +1285,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>368307.9016518379</v>
+        <v>367788</v>
       </c>
       <c r="R8" t="n">
-        <v>6940670.373729251</v>
+        <v>6941012</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1483,19 +1343,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,15 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102149761</v>
+        <v>102149526</v>
       </c>
       <c r="B9" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1563,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>368074.6174278922</v>
+        <v>367927</v>
       </c>
       <c r="R9" t="n">
-        <v>6940939.4380741</v>
+        <v>6941012</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1596,19 +1441,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,52 +1470,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102146618</v>
+        <v>102150705</v>
       </c>
       <c r="B10" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>368162.7208526242</v>
+        <v>368157</v>
       </c>
       <c r="R10" t="n">
-        <v>6940784.584540918</v>
+        <v>6940883</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1710,19 +1539,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,52 +1568,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102145906</v>
+        <v>102150860</v>
       </c>
       <c r="B11" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>368354.2083946368</v>
+        <v>368203</v>
       </c>
       <c r="R11" t="n">
-        <v>6940661.15096398</v>
+        <v>6940890</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1824,19 +1637,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,15 +1666,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102151305</v>
+        <v>102146268</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,21 +1677,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1904,10 +1702,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>368264.5509692759</v>
+        <v>368289</v>
       </c>
       <c r="R12" t="n">
-        <v>6940788.841321145</v>
+        <v>6940710</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1937,19 +1735,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,15 +1764,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102150896</v>
+        <v>102147953</v>
       </c>
       <c r="B13" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,35 +1775,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>368196.0925193144</v>
+        <v>367822</v>
       </c>
       <c r="R13" t="n">
-        <v>6940891.692884291</v>
+        <v>6940973</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2050,19 +1833,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2089,55 +1862,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102147990</v>
+        <v>1048523</v>
       </c>
       <c r="B14" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220686</v>
+        <v>3277</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallen NNV, mellan Vivallen och Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>367835.3045088804</v>
+        <v>368178</v>
       </c>
       <c r="R14" t="n">
-        <v>6940975.273758898</v>
+        <v>6940847</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2161,22 +1927,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1979-08-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1979-08-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Leg. Stig Jacobsson.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,70 +1949,73 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av lövträd</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Dan Olofsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Stig Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Stig Jacobssons dagböcker</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102149726</v>
+        <v>1064323</v>
       </c>
       <c r="B15" t="n">
-        <v>96242</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219788</v>
+        <v>3528</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Vitterspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Cortinarius agathosmus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Brandrud, H.Lindstr. &amp; Melot</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallen NNV, mellan Vivallen och Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>368063.4506239234</v>
+        <v>368178</v>
       </c>
       <c r="R15" t="n">
-        <v>6940949.110912736</v>
+        <v>6940847</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2275,22 +2039,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-08-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-08-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Leg. Stig Jacobsson.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,30 +2061,35 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av lövträd</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr"/>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Dan Olofsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Stig Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Stig Jacobssons dagböcker</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102146400</v>
+        <v>1232067</v>
       </c>
       <c r="B16" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87563</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,38 +2097,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>3639</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rutspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cortinarius ionophyllus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Vivallen NNV, mellan Vivallen och Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>368246.468915417</v>
+        <v>368178</v>
       </c>
       <c r="R16" t="n">
-        <v>6940717.575568691</v>
+        <v>6940847</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2388,22 +2151,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-08-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-08-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Leg. Stig Jacobsson.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,30 +2173,35 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av lövträd</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Dan Olofsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Stig Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Stig Jacobssons dagböcker</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102151152</v>
+        <v>1250705</v>
       </c>
       <c r="B17" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2446,38 +2209,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>4404</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Vivallen NNV, mellan Vivallen och Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>368229.1437691518</v>
+        <v>368178</v>
       </c>
       <c r="R17" t="n">
-        <v>6940828.086260485</v>
+        <v>6940847</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2501,22 +2263,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1980-08-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1980-08-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Leg. Stig Jacobsson.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2528,69 +2285,73 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av lövträd</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Dan Olofsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Stig Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Stig Jacobssons dagböcker</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102148453</v>
+        <v>1311820</v>
       </c>
       <c r="B18" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallen NNV, mellan Vivallen och Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>367833.2592007</v>
+        <v>368178</v>
       </c>
       <c r="R18" t="n">
-        <v>6941063.022782722</v>
+        <v>6940847</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2614,22 +2375,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1979-08-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1979-08-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Leg. Stig Jacobsson.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2641,66 +2397,71 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av lövträd</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr"/>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Dan Olofsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Stig Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Stig Jacobssons dagböcker</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102148400</v>
+        <v>102145976</v>
       </c>
       <c r="B19" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>367864.4641594911</v>
+        <v>368325</v>
       </c>
       <c r="R19" t="n">
-        <v>6941057.6258063</v>
+        <v>6940662</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2730,19 +2491,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2769,19 +2520,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102148037</v>
+        <v>102146963</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2810,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>367837.4805561956</v>
+        <v>368016</v>
       </c>
       <c r="R20" t="n">
-        <v>6940983.492415531</v>
+        <v>6940896</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2843,19 +2589,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,51 +2618,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102150766</v>
+        <v>102147806</v>
       </c>
       <c r="B21" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>368193.6076715121</v>
+        <v>367830</v>
       </c>
       <c r="R21" t="n">
-        <v>6940933.78073218</v>
+        <v>6940949</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2956,19 +2687,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2995,37 +2716,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102148445</v>
+        <v>102147890</v>
       </c>
       <c r="B22" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3036,10 +2752,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>367833.2592007</v>
+        <v>367829</v>
       </c>
       <c r="R22" t="n">
-        <v>6941063.022782722</v>
+        <v>6940954</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3069,19 +2785,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3108,52 +2814,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102149868</v>
+        <v>102148037</v>
       </c>
       <c r="B23" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>368092.0604841363</v>
+        <v>367837</v>
       </c>
       <c r="R23" t="n">
-        <v>6940994.574576947</v>
+        <v>6940984</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3183,19 +2883,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3222,51 +2912,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>102146268</v>
+        <v>102148271</v>
       </c>
       <c r="B24" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>368288.6774061533</v>
+        <v>367848</v>
       </c>
       <c r="R24" t="n">
-        <v>6940709.899196514</v>
+        <v>6941037</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3296,19 +2981,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3335,57 +3010,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102148953</v>
+        <v>102149467</v>
       </c>
       <c r="B25" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>367788.720085277</v>
+        <v>367887</v>
       </c>
       <c r="R25" t="n">
-        <v>6941023.734357146</v>
+        <v>6941009</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3415,19 +3079,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3454,51 +3108,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>102151142</v>
+        <v>102149627</v>
       </c>
       <c r="B26" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>368211.2789835564</v>
+        <v>368034</v>
       </c>
       <c r="R26" t="n">
-        <v>6940832.02659352</v>
+        <v>6940953</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3528,19 +3177,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3567,51 +3206,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>102145792</v>
+        <v>102149675</v>
       </c>
       <c r="B27" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>368287.4946732124</v>
+        <v>368035</v>
       </c>
       <c r="R27" t="n">
-        <v>6940715.022085576</v>
+        <v>6940966</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3641,19 +3275,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3680,52 +3304,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>102145795</v>
+        <v>102150264</v>
       </c>
       <c r="B28" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>368287.4946732124</v>
+        <v>368089</v>
       </c>
       <c r="R28" t="n">
-        <v>6940715.022085576</v>
+        <v>6940912</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3755,19 +3373,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3794,57 +3402,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>102145890</v>
+        <v>102150659</v>
       </c>
       <c r="B29" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>368358.8732004403</v>
+        <v>368153</v>
       </c>
       <c r="R29" t="n">
-        <v>6940673.886280463</v>
+        <v>6940886</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3874,19 +3471,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3913,51 +3500,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>102149526</v>
+        <v>102150736</v>
       </c>
       <c r="B30" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>367926.8813927446</v>
+        <v>368177</v>
       </c>
       <c r="R30" t="n">
-        <v>6941012.227061708</v>
+        <v>6940916</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3987,19 +3569,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4026,51 +3598,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>102148447</v>
+        <v>102151305</v>
       </c>
       <c r="B31" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>367833.2592007</v>
+        <v>368265</v>
       </c>
       <c r="R31" t="n">
-        <v>6941063.022782722</v>
+        <v>6940789</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4100,19 +3667,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4139,37 +3696,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>102146223</v>
+        <v>102151426</v>
       </c>
       <c r="B32" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4180,10 +3732,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>368299.9958290507</v>
+        <v>368294</v>
       </c>
       <c r="R32" t="n">
-        <v>6940692.375937462</v>
+        <v>6940766</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4213,19 +3765,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4252,15 +3794,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>102150264</v>
+        <v>102145792</v>
       </c>
       <c r="B33" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,35 +3805,35 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>368089.2579590661</v>
+        <v>368287</v>
       </c>
       <c r="R33" t="n">
-        <v>6940912.554519196</v>
+        <v>6940715</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4326,19 +3863,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4365,15 +3892,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>102146864</v>
+        <v>102146201</v>
       </c>
       <c r="B34" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4381,35 +3903,35 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>368068.2451904673</v>
+        <v>368308</v>
       </c>
       <c r="R34" t="n">
-        <v>6940814.184306365</v>
+        <v>6940670</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4439,19 +3961,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4478,52 +3990,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>102147528</v>
+        <v>102146223</v>
       </c>
       <c r="B35" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>367859.5718283363</v>
+        <v>368300</v>
       </c>
       <c r="R35" t="n">
-        <v>6940969.691933472</v>
+        <v>6940692</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4553,19 +4059,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4592,15 +4088,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>102146309</v>
+        <v>102146272</v>
       </c>
       <c r="B36" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,21 +4099,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4633,10 +4124,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>368258.5231615495</v>
+        <v>368289</v>
       </c>
       <c r="R36" t="n">
-        <v>6940706.944626286</v>
+        <v>6940710</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4666,19 +4157,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4705,15 +4186,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>102148271</v>
+        <v>102146400</v>
       </c>
       <c r="B37" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4721,35 +4197,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>367848.8382682432</v>
+        <v>368246</v>
       </c>
       <c r="R37" t="n">
-        <v>6941036.562915049</v>
+        <v>6940718</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4779,19 +4255,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4818,51 +4284,46 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>102149265</v>
+        <v>102146529</v>
       </c>
       <c r="B38" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>367770.2134342007</v>
+        <v>368233</v>
       </c>
       <c r="R38" t="n">
-        <v>6941011.55328278</v>
+        <v>6940754</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4892,19 +4353,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4931,15 +4382,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>102149525</v>
+        <v>102146862</v>
       </c>
       <c r="B39" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4972,10 +4418,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>367926.8813927446</v>
+        <v>368069</v>
       </c>
       <c r="R39" t="n">
-        <v>6941012.227061708</v>
+        <v>6940814</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5005,19 +4451,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5044,15 +4480,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>102151763</v>
+        <v>102146883</v>
       </c>
       <c r="B40" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5081,14 +4512,14 @@
       <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>368321.0393905282</v>
+        <v>368053</v>
       </c>
       <c r="R40" t="n">
-        <v>6940733.531231986</v>
+        <v>6940853</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5118,19 +4549,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5157,15 +4578,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>102146862</v>
+        <v>102146925</v>
       </c>
       <c r="B41" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5198,10 +4614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>368068.2451904673</v>
+        <v>368035</v>
       </c>
       <c r="R41" t="n">
-        <v>6940814.184306365</v>
+        <v>6940861</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5231,19 +4647,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5270,15 +4676,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>102146529</v>
+        <v>102147104</v>
       </c>
       <c r="B42" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5307,14 +4708,14 @@
       <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>368233.1519065168</v>
+        <v>368004</v>
       </c>
       <c r="R42" t="n">
-        <v>6940754.558870765</v>
+        <v>6940998</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5344,19 +4745,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5383,52 +4774,46 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>102146949</v>
+        <v>102147511</v>
       </c>
       <c r="B43" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>368022.1267274416</v>
+        <v>367860</v>
       </c>
       <c r="R43" t="n">
-        <v>6940897.693179706</v>
+        <v>6940970</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5458,19 +4843,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5497,52 +4872,46 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>102146228</v>
+        <v>102148447</v>
       </c>
       <c r="B44" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221946</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>368299.9958290507</v>
+        <v>367833</v>
       </c>
       <c r="R44" t="n">
-        <v>6940692.375937462</v>
+        <v>6941063</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5572,19 +4941,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5611,15 +4970,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>102149449</v>
+        <v>102148905</v>
       </c>
       <c r="B45" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5652,10 +5006,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>367821.4459463539</v>
+        <v>367807</v>
       </c>
       <c r="R45" t="n">
-        <v>6940975.36505076</v>
+        <v>6941042</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5685,19 +5039,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5724,15 +5068,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>102150860</v>
+        <v>102149449</v>
       </c>
       <c r="B46" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5740,35 +5079,35 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>368203.4558110099</v>
+        <v>367822</v>
       </c>
       <c r="R46" t="n">
-        <v>6940890.938635924</v>
+        <v>6940975</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5798,19 +5137,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5837,15 +5166,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>102150303</v>
+        <v>102149455</v>
       </c>
       <c r="B47" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5878,10 +5202,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>368088.4298800746</v>
+        <v>367879</v>
       </c>
       <c r="R47" t="n">
-        <v>6940903.359081805</v>
+        <v>6940975</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5911,19 +5235,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5950,52 +5264,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>102150904</v>
+        <v>102149525</v>
       </c>
       <c r="B48" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>368204.5284170775</v>
+        <v>367927</v>
       </c>
       <c r="R48" t="n">
-        <v>6940883.051819292</v>
+        <v>6941012</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6025,19 +5333,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6064,52 +5362,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>102151156</v>
+        <v>102149709</v>
       </c>
       <c r="B49" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>368229.1437691518</v>
+        <v>368059</v>
       </c>
       <c r="R49" t="n">
-        <v>6940828.086260485</v>
+        <v>6940976</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6139,19 +5431,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6178,15 +5460,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>102150705</v>
+        <v>102149724</v>
       </c>
       <c r="B50" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6194,21 +5471,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6219,10 +5496,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>368157.415547943</v>
+        <v>368064</v>
       </c>
       <c r="R50" t="n">
-        <v>6940883.541426096</v>
+        <v>6940950</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6252,19 +5529,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6291,52 +5558,46 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>102150408</v>
+        <v>102149761</v>
       </c>
       <c r="B51" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>368085.9118819083</v>
+        <v>368075</v>
       </c>
       <c r="R51" t="n">
-        <v>6940863.315479978</v>
+        <v>6940939</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6366,19 +5627,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6405,15 +5656,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>102146848</v>
+        <v>102150303</v>
       </c>
       <c r="B52" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6421,21 +5667,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6446,10 +5692,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>368092.3856553845</v>
+        <v>368088</v>
       </c>
       <c r="R52" t="n">
-        <v>6940805.379064674</v>
+        <v>6940904</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6479,19 +5725,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6518,15 +5754,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>102146963</v>
+        <v>102150766</v>
       </c>
       <c r="B53" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6534,35 +5765,35 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>368016.4987927192</v>
+        <v>368194</v>
       </c>
       <c r="R53" t="n">
-        <v>6940895.610190081</v>
+        <v>6940934</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6592,19 +5823,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6631,15 +5852,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>102147523</v>
+        <v>102150896</v>
       </c>
       <c r="B54" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6647,35 +5863,35 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>367859.5718283363</v>
+        <v>368197</v>
       </c>
       <c r="R54" t="n">
-        <v>6940969.691933472</v>
+        <v>6940892</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6705,19 +5921,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6744,52 +5950,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>102147007</v>
+        <v>102151142</v>
       </c>
       <c r="B55" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>367987.2450435191</v>
+        <v>368211</v>
       </c>
       <c r="R55" t="n">
-        <v>6940915.232173959</v>
+        <v>6940832</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6819,19 +6019,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6858,52 +6048,46 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>102147973</v>
+        <v>102151280</v>
       </c>
       <c r="B56" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>367835.3045088804</v>
+        <v>368250</v>
       </c>
       <c r="R56" t="n">
-        <v>6940975.273758898</v>
+        <v>6940800</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6933,19 +6117,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6972,15 +6146,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>102149467</v>
+        <v>102151763</v>
       </c>
       <c r="B57" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6988,35 +6157,35 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>367887.0046318496</v>
+        <v>368322</v>
       </c>
       <c r="R57" t="n">
-        <v>6941008.741011174</v>
+        <v>6940734</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7046,19 +6215,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7085,15 +6244,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>102149709</v>
+        <v>102149395</v>
       </c>
       <c r="B58" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7101,21 +6255,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7126,10 +6280,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>368059.4029342853</v>
+        <v>367751</v>
       </c>
       <c r="R58" t="n">
-        <v>6940975.111167865</v>
+        <v>6941004</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7159,19 +6313,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7198,15 +6342,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>102149744</v>
+        <v>102149208</v>
       </c>
       <c r="B59" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7214,36 +6353,35 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>368071.5347298197</v>
+        <v>367772</v>
       </c>
       <c r="R59" t="n">
-        <v>6940943.252112151</v>
+        <v>6941011</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7273,19 +6411,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7312,51 +6440,46 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>102146883</v>
+        <v>102146192</v>
       </c>
       <c r="B60" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>6486</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>368052.6971552192</v>
+        <v>368309</v>
       </c>
       <c r="R60" t="n">
-        <v>6940853.101998584</v>
+        <v>6940667</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7386,26 +6509,16 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG60" t="b">
         <v>0</v>
@@ -7425,15 +6538,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>102146216</v>
+        <v>102146743</v>
       </c>
       <c r="B61" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7441,35 +6549,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>368304.7963987795</v>
+        <v>368114</v>
       </c>
       <c r="R61" t="n">
-        <v>6940685.263476986</v>
+        <v>6940782</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7499,19 +6613,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7538,15 +6642,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>102149019</v>
+        <v>102146904</v>
       </c>
       <c r="B62" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7554,35 +6653,41 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>367788.2422458101</v>
+        <v>368053</v>
       </c>
       <c r="R62" t="n">
-        <v>6941011.756801188</v>
+        <v>6940853</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7612,19 +6717,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7651,51 +6746,52 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>102149598</v>
+        <v>102149559</v>
       </c>
       <c r="B63" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229748</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>368003.192942782</v>
+        <v>367967</v>
       </c>
       <c r="R63" t="n">
-        <v>6940979.195133281</v>
+        <v>6940988</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7725,19 +6821,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7764,15 +6850,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102149208</v>
+        <v>102147181</v>
       </c>
       <c r="B64" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7780,35 +6861,41 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>367772.0220115775</v>
+        <v>367974</v>
       </c>
       <c r="R64" t="n">
-        <v>6941010.558301926</v>
+        <v>6941007</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7838,19 +6925,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7877,51 +6954,52 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102149724</v>
+        <v>102149337</v>
       </c>
       <c r="B65" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>368063.4506239234</v>
+        <v>367755</v>
       </c>
       <c r="R65" t="n">
-        <v>6940949.110912736</v>
+        <v>6941005</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7951,19 +7029,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7990,51 +7058,52 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>102146925</v>
+        <v>102148295</v>
       </c>
       <c r="B66" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>368035.9021293187</v>
+        <v>367849</v>
       </c>
       <c r="R66" t="n">
-        <v>6940860.69210359</v>
+        <v>6941037</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8064,19 +7133,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8103,51 +7162,52 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>102147104</v>
+        <v>102148467</v>
       </c>
       <c r="B67" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>368003.9635794971</v>
+        <v>367817</v>
       </c>
       <c r="R67" t="n">
-        <v>6940998.543647709</v>
+        <v>6941073</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8177,19 +7237,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8216,15 +7266,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>102146290</v>
+        <v>102145890</v>
       </c>
       <c r="B68" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8232,36 +7277,41 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221725</v>
+        <v>105930</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>368272.9026842202</v>
+        <v>368359</v>
       </c>
       <c r="R68" t="n">
-        <v>6940696.682731867</v>
+        <v>6940674</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8291,19 +7341,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8330,15 +7370,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>102146535</v>
+        <v>102148953</v>
       </c>
       <c r="B69" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,36 +7381,41 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221725</v>
+        <v>105930</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>368233.1519065168</v>
+        <v>367789</v>
       </c>
       <c r="R69" t="n">
-        <v>6940754.558870765</v>
+        <v>6941023</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8405,19 +7445,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8444,51 +7474,47 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>102148905</v>
+        <v>102149726</v>
       </c>
       <c r="B70" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>219788</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>367807.4654836587</v>
+        <v>368064</v>
       </c>
       <c r="R70" t="n">
-        <v>6941041.904222713</v>
+        <v>6940950</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8518,19 +7544,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8560,12 +7576,7 @@
         <v>102149727</v>
       </c>
       <c r="B71" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8599,10 +7610,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>368063.4506239234</v>
+        <v>368064</v>
       </c>
       <c r="R71" t="n">
-        <v>6940949.110912736</v>
+        <v>6940950</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8632,19 +7643,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8671,51 +7672,47 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>102149627</v>
+        <v>102149868</v>
       </c>
       <c r="B72" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>368033.5550572069</v>
+        <v>368093</v>
       </c>
       <c r="R72" t="n">
-        <v>6940952.608280179</v>
+        <v>6940995</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8745,19 +7742,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8784,51 +7771,47 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>102149455</v>
+        <v>102147990</v>
       </c>
       <c r="B73" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>220686</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>367879.6482212635</v>
+        <v>367835</v>
       </c>
       <c r="R73" t="n">
-        <v>6940974.889877694</v>
+        <v>6940975</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8858,19 +7841,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8897,51 +7870,47 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>102150659</v>
+        <v>102150187</v>
       </c>
       <c r="B74" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220686</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>368153.3366906127</v>
+        <v>368092</v>
       </c>
       <c r="R74" t="n">
-        <v>6940885.549379623</v>
+        <v>6941031</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8971,19 +7940,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9010,15 +7969,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>102150255</v>
+        <v>102145906</v>
       </c>
       <c r="B75" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9026,21 +7980,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9048,14 +8002,14 @@
       <c r="L75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>368083.0558100979</v>
+        <v>368354</v>
       </c>
       <c r="R75" t="n">
-        <v>6940919.261247566</v>
+        <v>6940661</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9085,19 +8039,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9124,51 +8068,47 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>102150736</v>
+        <v>102146290</v>
       </c>
       <c r="B76" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>368177.1706535198</v>
+        <v>368273</v>
       </c>
       <c r="R76" t="n">
-        <v>6940915.516419369</v>
+        <v>6940697</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9198,19 +8138,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9237,51 +8167,47 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>102149675</v>
+        <v>102146535</v>
       </c>
       <c r="B77" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>368034.5483809388</v>
+        <v>368233</v>
       </c>
       <c r="R77" t="n">
-        <v>6940965.949715935</v>
+        <v>6940754</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9311,19 +8237,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9350,51 +8266,47 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>102146272</v>
+        <v>102146228</v>
       </c>
       <c r="B78" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6440</v>
+        <v>221946</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>368288.6774061533</v>
+        <v>368300</v>
       </c>
       <c r="R78" t="n">
-        <v>6940709.899196514</v>
+        <v>6940692</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9424,19 +8336,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9463,51 +8365,47 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>102146990</v>
+        <v>102145795</v>
       </c>
       <c r="B79" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>368007.3792173262</v>
+        <v>368287</v>
       </c>
       <c r="R79" t="n">
-        <v>6940910.27744741</v>
+        <v>6940715</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9537,19 +8435,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9576,51 +8464,47 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>102147953</v>
+        <v>102146022</v>
       </c>
       <c r="B80" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1467</v>
+        <v>221952</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>367821.3173297494</v>
+        <v>368321</v>
       </c>
       <c r="R80" t="n">
-        <v>6940972.140281803</v>
+        <v>6940662</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9650,19 +8534,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9689,51 +8563,47 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>102151280</v>
+        <v>102146618</v>
       </c>
       <c r="B81" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vivallsvägen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>368249.2674710115</v>
+        <v>368163</v>
       </c>
       <c r="R81" t="n">
-        <v>6940799.6003743</v>
+        <v>6940784</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9763,19 +8633,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9802,15 +8662,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>102150029</v>
+        <v>102146949</v>
       </c>
       <c r="B82" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9844,10 +8699,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>368095.7086206645</v>
+        <v>368023</v>
       </c>
       <c r="R82" t="n">
-        <v>6941016.576874249</v>
+        <v>6940898</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9877,19 +8732,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9916,51 +8761,47 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>102149466</v>
+        <v>102147007</v>
       </c>
       <c r="B83" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>367887.0046318496</v>
+        <v>367987</v>
       </c>
       <c r="R83" t="n">
-        <v>6941008.741011174</v>
+        <v>6940916</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9990,19 +8831,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10029,57 +8860,47 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>102148295</v>
+        <v>102147528</v>
       </c>
       <c r="B84" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>367848.8382682432</v>
+        <v>367860</v>
       </c>
       <c r="R84" t="n">
-        <v>6941036.562915049</v>
+        <v>6940970</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10109,19 +8930,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10148,57 +8959,47 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>102148467</v>
+        <v>102147973</v>
       </c>
       <c r="B85" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>367817.0189056296</v>
+        <v>367835</v>
       </c>
       <c r="R85" t="n">
-        <v>6941072.898535693</v>
+        <v>6940975</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10228,19 +9029,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10267,57 +9058,47 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>102146904</v>
+        <v>102149744</v>
       </c>
       <c r="B86" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>368052.6971552192</v>
+        <v>368072</v>
       </c>
       <c r="R86" t="n">
-        <v>6940853.101998584</v>
+        <v>6940943</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10347,19 +9128,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10386,57 +9157,47 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>102149559</v>
+        <v>102150029</v>
       </c>
       <c r="B87" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>367967.0408363842</v>
+        <v>368096</v>
       </c>
       <c r="R87" t="n">
-        <v>6940988.017813699</v>
+        <v>6941017</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10466,19 +9227,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10505,57 +9256,47 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>102146743</v>
+        <v>102150255</v>
       </c>
       <c r="B88" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>368113.6327688551</v>
+        <v>368083</v>
       </c>
       <c r="R88" t="n">
-        <v>6940781.923170613</v>
+        <v>6940920</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10585,19 +9326,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10624,59 +9355,50 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129218118</v>
+        <v>102150408</v>
       </c>
       <c r="B89" t="n">
-        <v>91577</v>
+        <v>99140</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1108</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>368107</v>
+        <v>368086</v>
       </c>
       <c r="R89" t="n">
-        <v>6940826</v>
+        <v>6940864</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10700,12 +9422,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10714,22 +9436,415 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Herbert Baumann</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Herbert Baumann, Kerstin Baumann</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>102150904</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>368204</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6940883</v>
+      </c>
+      <c r="S90" t="n">
+        <v>25</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>102151156</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Vivallsvägen, Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>368229</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6940829</v>
+      </c>
+      <c r="S91" t="n">
+        <v>25</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>102149265</v>
+      </c>
+      <c r="B92" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>367770</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6941012</v>
+      </c>
+      <c r="S92" t="n">
+        <v>25</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>102149598</v>
+      </c>
+      <c r="B93" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>368004</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6940979</v>
+      </c>
+      <c r="S93" t="n">
+        <v>25</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28769-2022 artfynd.xlsx
+++ b/artfynd/A 28769-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AZ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129218118</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146309</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146848</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146864</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102147811</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102148453</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149019</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149526</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102150705</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1663,6 +1713,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102150860</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1761,6 +1816,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146268</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1859,6 +1919,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102147953</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1971,6 +2036,11 @@
           <t>Stig Jacobssons dagböcker</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1048523</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2083,6 +2153,11 @@
           <t>Stig Jacobssons dagböcker</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1064323</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2195,6 +2270,11 @@
           <t>Stig Jacobssons dagböcker</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1232067</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2307,6 +2387,11 @@
           <t>Stig Jacobssons dagböcker</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1250705</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2419,6 +2504,11 @@
           <t>Stig Jacobssons dagböcker</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1311820</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2517,6 +2607,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102145976</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2615,6 +2710,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146963</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2713,6 +2813,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102147806</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2811,6 +2916,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102147890</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2909,6 +3019,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102148037</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3007,6 +3122,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102148271</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3105,6 +3225,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149467</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3203,6 +3328,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149627</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3301,6 +3431,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149675</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3399,6 +3534,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102150264</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3497,6 +3637,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102150659</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3595,6 +3740,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102150736</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3693,6 +3843,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102151305</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3791,6 +3946,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102151426</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3889,6 +4049,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102145792</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3987,6 +4152,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146201</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4085,6 +4255,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146223</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4183,6 +4358,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146272</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4281,6 +4461,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146400</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4379,6 +4564,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146529</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4477,6 +4667,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146862</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4575,6 +4770,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146883</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4673,6 +4873,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146925</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4771,6 +4976,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102147104</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4869,6 +5079,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102147511</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4967,6 +5182,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102148447</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5065,6 +5285,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102148905</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5163,6 +5388,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149449</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5261,6 +5491,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149455</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5359,6 +5594,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149525</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5457,6 +5697,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149709</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5555,6 +5800,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149724</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5653,6 +5903,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149761</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5751,6 +6006,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102150303</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5849,6 +6109,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102150766</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5947,6 +6212,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102150896</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6045,6 +6315,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102151142</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6143,6 +6418,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102151280</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6241,6 +6521,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102151763</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6339,6 +6624,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149395</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6437,6 +6727,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149208</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6535,6 +6830,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146192</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6639,6 +6939,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146743</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6743,6 +7048,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146904</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6847,6 +7157,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149559</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6951,6 +7266,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102147181</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7055,6 +7375,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149337</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7159,6 +7484,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102148295</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7263,6 +7593,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102148467</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7367,6 +7702,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102145890</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7471,6 +7811,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102148953</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7570,6 +7915,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149726</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7669,6 +8019,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149727</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7768,6 +8123,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149868</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7867,6 +8227,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102147990</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7966,6 +8331,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102150187</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8065,6 +8435,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102145906</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8164,6 +8539,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146290</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8263,6 +8643,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146535</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8362,6 +8747,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146228</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8461,6 +8851,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102145795</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8560,6 +8955,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146022</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8659,6 +9059,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146618</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8758,6 +9163,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102146949</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8857,6 +9267,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102147007</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8956,6 +9371,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102147528</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9055,6 +9475,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102147973</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9154,6 +9579,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149744</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9253,6 +9683,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102150029</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9352,6 +9787,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102150255</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9451,6 +9891,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102150408</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9550,6 +9995,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102150904</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9649,6 +10099,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102151156</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9747,6 +10202,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149265</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9845,8 +10305,107 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102149598</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>